--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>15/08 22:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>35</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>16/08 17:15</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>16/08 21:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>09/08 20:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>10/08 12:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>18/08 00:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>16/08 00:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>45</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>09/08 03:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>09/08 17:20</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>60</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>13/08 00:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>09/08 21:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>15/08 17:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>14/08 18:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>40</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>12/08 18:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>55</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>10/08 09:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>50</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>10/08 12:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>50</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>09/08 23:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F21" t="n">
+        <v>3.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>10/08 14:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F22" t="n">
+        <v>2.95</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>17/08 19:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>50</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>14/08 00:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>09/08 16:10</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>6.70</t>
-        </is>
+      <c r="F25" t="n">
+        <v>6.7</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45878.0764820617</v>
+        <v>45878.07648206018</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,201 @@
           <t>16/08 19:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>45</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+3,89%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45878.07648206018</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Slovan </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FC Slovan Liberec – FK Dukla PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>09/08 15:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+3,89%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45878.0764820617</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+12,3%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45878.14047105527</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Northampto</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Northampton Town – SouthamptonEFL Cup</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>12/08 18:45</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+7,35%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45878.14047105527</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | The New Sa</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>The New Saints – Briton FerryCymru Premier - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10/08 13:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+4,75%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45878.14047105527</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Gremio – S</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gremio – Sport RecifeSérie A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10/08 23:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,90%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+4,49%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45878.14047105527</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>45</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45878.14047105527</v>
+        <v>45878.14047105324</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>12/08 18:45</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>50</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45878.14047105527</v>
+        <v>45878.14047105324</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>10/08 13:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>50</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45878.14047105527</v>
+        <v>45878.14047105324</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>10/08 23:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>55</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,52 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45878.14047105527</v>
+        <v>45878.14047105324</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tir cadré | Chicago Fi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chicago Fire – Los Angeles FCÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10/08 00:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+3,30%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45878.18845625838</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>10/08 00:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,142 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45878.18845625838</v>
+        <v>45878.18845626157</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – TSC Backa TopolaSuperLiga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>09/08 18:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+20,8%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45878.22371910657</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Shelbourne</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Shelbourne FC – HNK RijekaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>12/08 18:45</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+12,7%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45878.22371910657</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Volleyball | H 1 (+9.5)1er set | Géorgie – </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PMU(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Géorgie – GrèceVolleyball. Euro (QH)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>H 1 (+9.5)1er set</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>09/08 15:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+7,94%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45878.22371910657</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>09/08 18:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>55</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45878.22371910657</v>
+        <v>45878.2237191088</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>12/08 18:45</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>45</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45878.22371910657</v>
+        <v>45878.2237191088</v>
       </c>
     </row>
     <row r="34">
@@ -1885,10 +1881,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.26</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1901,7 +1895,277 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45878.22371910657</v>
+        <v>45878.2237191088</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | RB Salzbou</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RB Salzbourg – Grazer AKBundesliga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>09/08 17:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+40,1%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45878.27307556458</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | PSV Eindho</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven – Sparta RotterdamEredivisie</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>09/08 19:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>80.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+28,2%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45878.27307556458</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Standard L</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Standard Liège – GenkBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10/08 16:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>44,9%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+25,6%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45878.27307556458</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cruzeiro – SantosBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10/08 21:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>34,8%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+25,2%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45878.27307556458</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 29.5 - tirs | Vasco de G</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Vasco de Gama – Atletico MineiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 29.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10/08 19:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+24,8%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45878.27307556458</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 9.5 - tir cadré | Gremio RS </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Gremio RS – Sport RecifeBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10/08 23:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+15,7%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45878.27307556458</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>09/08 17:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>60</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45878.27307556458</v>
+        <v>45878.27307556713</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>09/08 19:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>80.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>80</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45878.27307556458</v>
+        <v>45878.27307556713</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>10/08 16:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.8</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45878.27307556458</v>
+        <v>45878.27307556713</v>
       </c>
     </row>
     <row r="38">
@@ -2059,10 +2053,8 @@
           <t>10/08 21:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F38" t="n">
+        <v>3.6</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2075,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45878.27307556458</v>
+        <v>45878.27307556713</v>
       </c>
     </row>
     <row r="39">
@@ -2104,10 +2096,8 @@
           <t>10/08 19:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.85</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45878.27307556458</v>
+        <v>45878.27307556713</v>
       </c>
     </row>
     <row r="40">
@@ -2149,23 +2139,156 @@
           <t>10/08 23:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+15,7%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45878.27307556713</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Napreda</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FK Napredak – Partizan BelgradeSuperLiga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10/08 18:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+12,9%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45878.30611956588</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tirs1re équipe | Zwolle – T</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Zwolle – TwentePays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10/08 10:15</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>2.80</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>41,3%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>+15,7%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>45878.27307556458</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45878.30611956588</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 25.5 - tirs | Ajax Amste</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam – TelstarPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10/08 12:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>36,5%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+9,62%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45878.30611956588</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>10/08 18:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>45</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45878.30611956588</v>
+        <v>45878.30611956018</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>10/08 10:15</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.8</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45878.30611956588</v>
+        <v>45878.30611956018</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>10/08 12:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,97 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45878.30611956588</v>
+        <v>45878.30611956018</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Stefanos T</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Stefanos Tsitsipas – Fabian MarozsanATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>09/08 16:10</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>30,1%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+50,4%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45878.35300477507</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Philadelph</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Philadelphia Union – Toronto FCMLS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>09/08 23:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+9,61%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45878.35300477507</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>09/08 16:10</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45878.35300477507</v>
+        <v>45878.3530047801</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>09/08 23:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>55</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,232 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45878.35300477507</v>
+        <v>45878.3530047801</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | Pavlyuchen</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pavlyuchenkova – A.Ito385076e7 WTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>09/08 15:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+34,3%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45878.39092332469</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | T.Maria – </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>T.Maria – M.KostyukWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>09/08 15:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+32,3%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45878.39092332469</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 1.5 - aces1er participant | Pedro Mart</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pedro Martinez – Tommy PaulATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 1.5 - aces1er participant</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>09/08 16:10</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>48,5%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45878.39092332469</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 5.5 | Instituto </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Instituto AC Cordoba – CA PlatenseLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>10/08 20:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+12,5%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45878.39092332469</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Anderlecht</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Anderlecht – Zulte WaregemBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>10/08 14:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+9,17%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45878.39092332469</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="F46" t="n">
+        <v>4.75</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45878.39092332469</v>
+        <v>45878.39092332176</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45878.39092332469</v>
+        <v>45878.39092332176</v>
       </c>
     </row>
     <row r="48">
@@ -2487,10 +2483,8 @@
           <t>09/08 16:10</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2.35</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2503,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45878.39092332469</v>
+        <v>45878.39092332176</v>
       </c>
     </row>
     <row r="49">
@@ -2532,10 +2526,8 @@
           <t>10/08 20:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>65</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2548,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45878.39092332469</v>
+        <v>45878.39092332176</v>
       </c>
     </row>
     <row r="50">
@@ -2577,10 +2569,8 @@
           <t>10/08 14:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F50" t="n">
+        <v>3.7</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2593,7 +2583,142 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45878.39092332469</v>
+        <v>45878.39092332176</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Kashiwa Re</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol – Shonan BellmareJ-League</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>10/08 10:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+29,5%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45878.43289362971</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | T.Fritz – </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>T.Fritz – E.NavaATP - Cincinnati H</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>10/08 00:10</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>45,9%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+28,6%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45878.43289362971</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atlético B</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga – Santa FePrimera A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10/08 00:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45878.43289362971</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>10/08 10:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>60</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45878.43289362971</v>
+        <v>45878.43289363426</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>10/08 00:10</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.8</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45878.43289362971</v>
+        <v>45878.43289363426</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>10/08 00:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>45</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,52 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45878.43289362971</v>
+        <v>45878.43289363426</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Jeonbuk Mo</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors – Daegu FCK League 1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>16/08 10:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+25,3%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45878.47134969095</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -2741,10 +2741,8 @@
           <t>16/08 10:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>60</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45878.47134969095</v>
+        <v>45878.4713496875</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2758,6 +2758,51 @@
         <v>45878.4713496875</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tir cadré | NEC Nimègu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NEC Nimègue – SBV ExcelsiorPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>09/08 14:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>31,6%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45878.56369479164</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>09/08 14:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F55" t="n">
+        <v>3.5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,52 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45878.56369479164</v>
+        <v>45878.56369479166</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Vissel Kob</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Vissel Kobe – Yokohama FCJ-League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>16/08 10:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+46,1%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45878.59752849142</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,23 +2827,111 @@
           <t>16/08 10:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>60</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+46,1%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45878.59752849537</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Istra 1961</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Istra 1961 – Lokomotiva ZagrebHNL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>09/08 16:15</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+38,0%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45878.64063488772</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Univers</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FC Universitatea Cluj – FC Petrolul PloiestiLiga 1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>09/08 18:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>+46,1%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>45878.59752849142</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+35,4%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45878.64063488772</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -2870,10 +2870,8 @@
           <t>09/08 16:15</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>55</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45878.64063488772</v>
+        <v>45878.64063488426</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>09/08 18:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>60</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45878.64063488772</v>
+        <v>45878.64063488426</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2930,6 +2930,141 @@
         <v>45878.64063488426</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Halmstads </t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Halmstads BK – Malmo FFAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>16/08 13:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+27,7%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45878.72177210005</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Universita</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova – FC HermannstadtLiga 1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>10/08 15:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+16,9%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45878.72177210005</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Dukla P</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FK Dukla Prague – FC Viktoria PlzenSynot League A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>16/08 15:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+12,4%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45878.72177210005</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>16/08 13:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>60</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45878.72177210005</v>
+        <v>45878.7217720949</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>10/08 15:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>50</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45878.72177210005</v>
+        <v>45878.7217720949</v>
       </c>
     </row>
     <row r="61">
@@ -3046,10 +3042,8 @@
           <t>16/08 15:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>45</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3062,7 +3056,52 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45878.72177210005</v>
+        <v>45878.7217720949</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | TSV Hartbe</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TSV Hartberg – RB SalzbourgBundesliga</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>16/08 15:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+39,6%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45878.77215672881</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -3085,10 +3085,8 @@
           <t>16/08 15:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>60</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45878.77215672881</v>
+        <v>45878.77215672454</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3102,6 +3102,51 @@
         <v>45878.77215672454</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Terence At</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Terence Atmane – Flavio CobolliATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>09/08 21:40</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>39,8%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+7,56%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45878.85025070111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>09/08 21:40</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F63" t="n">
+        <v>2.7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,97 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45878.85025070111</v>
+        <v>45878.85025070602</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | America de</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>America de Cali – Deportes TolimaPrimera A</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>09/08 22:15</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+38,3%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45878.88937685022</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | Z.Bergs – </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Z.Bergs – L.SonegoATP - Cincinnati H</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>09/08 21:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>53,4%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+6,89%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45878.88937685022</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>09/08 22:15</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>60</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45878.88937685022</v>
+        <v>45878.88937685185</v>
       </c>
     </row>
     <row r="65">
@@ -3216,10 +3214,8 @@
           <t>09/08 21:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3232,7 +3228,97 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45878.88937685022</v>
+        <v>45878.88937685185</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Atletico T</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Atletico Tucuman – Rosario CentralLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>09/08 23:45</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+7,24%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45878.93168356642</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Jiri Lehec</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka – Tristan BoyerATP 1000 Cincinnati</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>10/08 15:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>18,1%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+6,86%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45878.93168356642</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-09.xlsx
+++ b/data/valuebets_database_2025-08-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>09/08 23:45</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>40</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45878.93168356642</v>
+        <v>45878.93168356481</v>
       </c>
     </row>
     <row r="67">
@@ -3302,10 +3300,8 @@
           <t>10/08 15:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
+      <c r="F67" t="n">
+        <v>5.9</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3318,7 +3314,142 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45878.93168356642</v>
+        <v>45878.93168356481</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 2.51er set2e participant | Daria Kasa</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Daria Kasatkina – Lucia BronzettiWTA 1000 Cincinnati</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Moins que 2.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>10/08 18:40</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+37,3%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45878.97333236686</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 7.5 - tir cadré1re équipe | New Englan</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>New England Revolution – DC UnitedÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 7.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>09/08 23:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+12,1%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45878.97333236686</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Karen Khac</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Karen Khachanov – Valentin RoyerATP 1000 Cincinnati</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>10/08 18:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+9,63%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45878.97333236686</v>
       </c>
     </row>
   </sheetData>
